--- a/astro-site/public/dl/plan-negocio-paellero-eventos/plan-financiero-paellero-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-paellero-eventos/plan-financiero-paellero-eventos.xlsx
@@ -14,7 +14,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mix B2C-B2B" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Resumen'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'P&amp;L Año 1'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Proyección 3 años'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Mix B2C-B2B'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'KPIs'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -535,7 +541,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -562,6 +568,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -618,7 +625,7 @@
       </c>
       <c r="E6" s="7">
         <f>D6/$D$15</f>
-        <v/>
+        <v>0.03678061445261791</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -643,7 +650,7 @@
       </c>
       <c r="E7" s="7">
         <f>D7/$D$15</f>
-        <v/>
+        <v>0.06274340112505408</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -668,7 +675,7 @@
       </c>
       <c r="E8" s="7">
         <f>D8/$D$15</f>
-        <v/>
+        <v>0.0540891389009087</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -693,7 +700,7 @@
       </c>
       <c r="E9" s="7">
         <f>D9/$D$15</f>
-        <v/>
+        <v>0.025097360450021637</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -718,7 +725,7 @@
       </c>
       <c r="E10" s="7">
         <f>D10/$D$15</f>
-        <v/>
+        <v>0.08005192557334487</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -743,7 +750,7 @@
       </c>
       <c r="E11" s="7">
         <f>D11/$D$15</f>
-        <v/>
+        <v>0.04110774556469061</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -768,7 +775,7 @@
       </c>
       <c r="E12" s="7">
         <f>D12/$D$15</f>
-        <v/>
+        <v>0.02942449156209433</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -793,7 +800,7 @@
       </c>
       <c r="E13" s="7">
         <f>D13/$D$15</f>
-        <v/>
+        <v>0.15144958892254434</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
@@ -818,7 +825,7 @@
       </c>
       <c r="E14" s="7">
         <f>D14/$D$15</f>
-        <v/>
+        <v>0.5192557334487234</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -834,15 +841,15 @@
       </c>
       <c r="B15" s="9">
         <f>SUM(B6:B14)</f>
-        <v/>
+        <v>3790.0</v>
       </c>
       <c r="C15" s="9">
         <f>SUM(C6:C14)</f>
-        <v/>
+        <v>9670.0</v>
       </c>
       <c r="D15" s="9">
         <f>SUM(D6:D14)</f>
-        <v/>
+        <v>23110.0</v>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
@@ -853,11 +860,20 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -865,7 +881,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -900,6 +916,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1016,7 +1033,7 @@
       </c>
       <c r="N5" s="12">
         <f>SUM(B5:M5)</f>
-        <v/>
+        <v>48450.0</v>
       </c>
     </row>
     <row r="6">
@@ -1063,7 +1080,7 @@
       </c>
       <c r="N6" s="12">
         <f>SUM(B6:M6)</f>
-        <v/>
+        <v>166500.0</v>
       </c>
     </row>
     <row r="7">
@@ -1074,57 +1091,58 @@
       </c>
       <c r="B7" s="14">
         <f>SUM(B5:B6)</f>
-        <v/>
+        <v>4550.0</v>
       </c>
       <c r="C7" s="14">
         <f>SUM(C5:C6)</f>
-        <v/>
+        <v>4550.0</v>
       </c>
       <c r="D7" s="14">
         <f>SUM(D5:D6)</f>
-        <v/>
+        <v>11800.0</v>
       </c>
       <c r="E7" s="14">
         <f>SUM(E5:E6)</f>
-        <v/>
+        <v>14500.0</v>
       </c>
       <c r="F7" s="14">
         <f>SUM(F5:F6)</f>
-        <v/>
+        <v>26300.0</v>
       </c>
       <c r="G7" s="14">
         <f>SUM(G5:G6)</f>
-        <v/>
+        <v>31700.0</v>
       </c>
       <c r="H7" s="14">
         <f>SUM(H5:H6)</f>
-        <v/>
+        <v>29000.0</v>
       </c>
       <c r="I7" s="14">
         <f>SUM(I5:I6)</f>
-        <v/>
+        <v>19050.0</v>
       </c>
       <c r="J7" s="14">
         <f>SUM(J5:J6)</f>
-        <v/>
+        <v>29000.0</v>
       </c>
       <c r="K7" s="14">
         <f>SUM(K5:K6)</f>
-        <v/>
+        <v>23600.0</v>
       </c>
       <c r="L7" s="14">
         <f>SUM(L5:L6)</f>
-        <v/>
+        <v>9100.0</v>
       </c>
       <c r="M7" s="14">
         <f>SUM(M5:M6)</f>
-        <v/>
+        <v>11800.0</v>
       </c>
       <c r="N7" s="14">
         <f>SUM(N5:N6)</f>
-        <v/>
-      </c>
-    </row>
+        <v>214950.0</v>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
@@ -1133,55 +1151,55 @@
       </c>
       <c r="B9" s="12">
         <f>B7*0.28</f>
-        <v/>
+        <v>1274.0000000000002</v>
       </c>
       <c r="C9" s="12">
         <f>C7*0.28</f>
-        <v/>
+        <v>1274.0000000000002</v>
       </c>
       <c r="D9" s="12">
         <f>D7*0.28</f>
-        <v/>
+        <v>3304.0000000000005</v>
       </c>
       <c r="E9" s="12">
         <f>E7*0.28</f>
-        <v/>
+        <v>4060.0000000000005</v>
       </c>
       <c r="F9" s="12">
         <f>F7*0.28</f>
-        <v/>
+        <v>7364.000000000001</v>
       </c>
       <c r="G9" s="12">
         <f>G7*0.28</f>
-        <v/>
+        <v>8876.0</v>
       </c>
       <c r="H9" s="12">
         <f>H7*0.28</f>
-        <v/>
+        <v>8120.000000000001</v>
       </c>
       <c r="I9" s="12">
         <f>I7*0.28</f>
-        <v/>
+        <v>5334.000000000001</v>
       </c>
       <c r="J9" s="12">
         <f>J7*0.28</f>
-        <v/>
+        <v>8120.000000000001</v>
       </c>
       <c r="K9" s="12">
         <f>K7*0.28</f>
-        <v/>
+        <v>6608.000000000001</v>
       </c>
       <c r="L9" s="12">
         <f>L7*0.28</f>
-        <v/>
+        <v>2548.0000000000005</v>
       </c>
       <c r="M9" s="12">
         <f>M7*0.28</f>
-        <v/>
+        <v>3304.0000000000005</v>
       </c>
       <c r="N9" s="12">
         <f>N7*0.28</f>
-        <v/>
+        <v>60186.00000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1192,55 +1210,55 @@
       </c>
       <c r="B10" s="12">
         <f>B7*0.05</f>
-        <v/>
+        <v>227.5</v>
       </c>
       <c r="C10" s="12">
         <f>C7*0.05</f>
-        <v/>
+        <v>227.5</v>
       </c>
       <c r="D10" s="12">
         <f>D7*0.05</f>
-        <v/>
+        <v>590.0</v>
       </c>
       <c r="E10" s="12">
         <f>E7*0.05</f>
-        <v/>
+        <v>725.0</v>
       </c>
       <c r="F10" s="12">
         <f>F7*0.05</f>
-        <v/>
+        <v>1315.0</v>
       </c>
       <c r="G10" s="12">
         <f>G7*0.05</f>
-        <v/>
+        <v>1585.0</v>
       </c>
       <c r="H10" s="12">
         <f>H7*0.05</f>
-        <v/>
+        <v>1450.0</v>
       </c>
       <c r="I10" s="12">
         <f>I7*0.05</f>
-        <v/>
+        <v>952.5</v>
       </c>
       <c r="J10" s="12">
         <f>J7*0.05</f>
-        <v/>
+        <v>1450.0</v>
       </c>
       <c r="K10" s="12">
         <f>K7*0.05</f>
-        <v/>
+        <v>1180.0</v>
       </c>
       <c r="L10" s="12">
         <f>L7*0.05</f>
-        <v/>
+        <v>455.0</v>
       </c>
       <c r="M10" s="12">
         <f>M7*0.05</f>
-        <v/>
+        <v>590.0</v>
       </c>
       <c r="N10" s="12">
         <f>N7*0.05</f>
-        <v/>
+        <v>10747.5</v>
       </c>
     </row>
     <row r="11">
@@ -1251,57 +1269,58 @@
       </c>
       <c r="B11" s="12">
         <f>B7*0.12</f>
-        <v/>
+        <v>546.0</v>
       </c>
       <c r="C11" s="12">
         <f>C7*0.12</f>
-        <v/>
+        <v>546.0</v>
       </c>
       <c r="D11" s="12">
         <f>D7*0.12</f>
-        <v/>
+        <v>1416.0</v>
       </c>
       <c r="E11" s="12">
         <f>E7*0.12</f>
-        <v/>
+        <v>1740.0</v>
       </c>
       <c r="F11" s="12">
         <f>F7*0.12</f>
-        <v/>
+        <v>3156.0</v>
       </c>
       <c r="G11" s="12">
         <f>G7*0.12</f>
-        <v/>
+        <v>3804.0</v>
       </c>
       <c r="H11" s="12">
         <f>H7*0.12</f>
-        <v/>
+        <v>3480.0</v>
       </c>
       <c r="I11" s="12">
         <f>I7*0.12</f>
-        <v/>
+        <v>2286.0</v>
       </c>
       <c r="J11" s="12">
         <f>J7*0.12</f>
-        <v/>
+        <v>3480.0</v>
       </c>
       <c r="K11" s="12">
         <f>K7*0.12</f>
-        <v/>
+        <v>2832.0</v>
       </c>
       <c r="L11" s="12">
         <f>L7*0.12</f>
-        <v/>
+        <v>1092.0</v>
       </c>
       <c r="M11" s="12">
         <f>M7*0.12</f>
-        <v/>
+        <v>1416.0</v>
       </c>
       <c r="N11" s="12">
         <f>N7*0.12</f>
-        <v/>
-      </c>
-    </row>
+        <v>25794.0</v>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -1346,7 +1365,7 @@
       </c>
       <c r="N13" s="12">
         <f>SUM(B13:M13)</f>
-        <v/>
+        <v>960.0</v>
       </c>
     </row>
     <row r="14">
@@ -1393,7 +1412,7 @@
       </c>
       <c r="N14" s="12">
         <f>SUM(B14:M14)</f>
-        <v/>
+        <v>1440.0</v>
       </c>
     </row>
     <row r="15">
@@ -1440,7 +1459,7 @@
       </c>
       <c r="N15" s="12">
         <f>SUM(B15:M15)</f>
-        <v/>
+        <v>2160.0</v>
       </c>
     </row>
     <row r="16">
@@ -1487,9 +1506,10 @@
       </c>
       <c r="N16" s="12">
         <f>SUM(B16:M16)</f>
-        <v/>
-      </c>
-    </row>
+        <v>3840.0</v>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
@@ -1498,55 +1518,55 @@
       </c>
       <c r="B18" s="14">
         <f>SUM(B9:B11)+SUM(B13:B16)</f>
-        <v/>
+        <v>2747.5</v>
       </c>
       <c r="C18" s="14">
         <f>SUM(C9:C11)+SUM(C13:C16)</f>
-        <v/>
+        <v>2747.5</v>
       </c>
       <c r="D18" s="14">
         <f>SUM(D9:D11)+SUM(D13:D16)</f>
-        <v/>
+        <v>6010.0</v>
       </c>
       <c r="E18" s="14">
         <f>SUM(E9:E11)+SUM(E13:E16)</f>
-        <v/>
+        <v>7225.0</v>
       </c>
       <c r="F18" s="14">
         <f>SUM(F9:F11)+SUM(F13:F16)</f>
-        <v/>
+        <v>12535.0</v>
       </c>
       <c r="G18" s="14">
         <f>SUM(G9:G11)+SUM(G13:G16)</f>
-        <v/>
+        <v>14965.0</v>
       </c>
       <c r="H18" s="14">
         <f>SUM(H9:H11)+SUM(H13:H16)</f>
-        <v/>
+        <v>13750.0</v>
       </c>
       <c r="I18" s="14">
         <f>SUM(I9:I11)+SUM(I13:I16)</f>
-        <v/>
+        <v>9272.5</v>
       </c>
       <c r="J18" s="14">
         <f>SUM(J9:J11)+SUM(J13:J16)</f>
-        <v/>
+        <v>13750.0</v>
       </c>
       <c r="K18" s="14">
         <f>SUM(K9:K11)+SUM(K13:K16)</f>
-        <v/>
+        <v>11320.0</v>
       </c>
       <c r="L18" s="14">
         <f>SUM(L9:L11)+SUM(L13:L16)</f>
-        <v/>
+        <v>4795.0</v>
       </c>
       <c r="M18" s="14">
         <f>SUM(M9:M11)+SUM(M13:M16)</f>
-        <v/>
+        <v>6010.0</v>
       </c>
       <c r="N18" s="14">
         <f>SUM(N9:N11)+SUM(N13:N16)</f>
-        <v/>
+        <v>105127.5</v>
       </c>
     </row>
     <row r="19">
@@ -1557,63 +1577,72 @@
       </c>
       <c r="B19" s="15">
         <f>B7-B18</f>
-        <v/>
+        <v>1802.5</v>
       </c>
       <c r="C19" s="15">
         <f>C7-C18</f>
-        <v/>
+        <v>1802.5</v>
       </c>
       <c r="D19" s="15">
         <f>D7-D18</f>
-        <v/>
+        <v>5790.0</v>
       </c>
       <c r="E19" s="15">
         <f>E7-E18</f>
-        <v/>
+        <v>7275.0</v>
       </c>
       <c r="F19" s="15">
         <f>F7-F18</f>
-        <v/>
+        <v>13765.0</v>
       </c>
       <c r="G19" s="15">
         <f>G7-G18</f>
-        <v/>
+        <v>16735.0</v>
       </c>
       <c r="H19" s="15">
         <f>H7-H18</f>
-        <v/>
+        <v>15250.0</v>
       </c>
       <c r="I19" s="15">
         <f>I7-I18</f>
-        <v/>
+        <v>9777.5</v>
       </c>
       <c r="J19" s="15">
         <f>J7-J18</f>
-        <v/>
+        <v>15250.0</v>
       </c>
       <c r="K19" s="15">
         <f>K7-K18</f>
-        <v/>
+        <v>12280.0</v>
       </c>
       <c r="L19" s="15">
         <f>L7-L18</f>
-        <v/>
+        <v>4305.0</v>
       </c>
       <c r="M19" s="15">
         <f>M7-M18</f>
-        <v/>
+        <v>5790.0</v>
       </c>
       <c r="N19" s="15">
         <f>N7-N18</f>
-        <v/>
+        <v>109822.5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1621,7 +1650,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1646,6 +1675,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1740,15 +1770,15 @@
       </c>
       <c r="B9" s="6">
         <f>B5*B7</f>
-        <v/>
+        <v>48450.0</v>
       </c>
       <c r="C9" s="6">
         <f>C5*C7</f>
-        <v/>
+        <v>66240.0</v>
       </c>
       <c r="D9" s="6">
         <f>D5*D7</f>
-        <v/>
+        <v>85140.0</v>
       </c>
     </row>
     <row r="10">
@@ -1759,15 +1789,15 @@
       </c>
       <c r="B10" s="6">
         <f>B6*B8</f>
-        <v/>
+        <v>166500.0</v>
       </c>
       <c r="C10" s="6">
         <f>C6*C8</f>
-        <v/>
+        <v>227700.0</v>
       </c>
       <c r="D10" s="6">
         <f>D6*D8</f>
-        <v/>
+        <v>289800.0</v>
       </c>
     </row>
     <row r="11">
@@ -1778,15 +1808,15 @@
       </c>
       <c r="B11" s="9">
         <f>B9+B10</f>
-        <v/>
+        <v>214950.0</v>
       </c>
       <c r="C11" s="9">
         <f>C9+C10</f>
-        <v/>
+        <v>293940.0</v>
       </c>
       <c r="D11" s="9">
         <f>D9+D10</f>
-        <v/>
+        <v>374940.0</v>
       </c>
     </row>
     <row r="12">
@@ -1797,15 +1827,15 @@
       </c>
       <c r="B12" s="6">
         <f>B11*0.28</f>
-        <v/>
+        <v>60186.00000000001</v>
       </c>
       <c r="C12" s="6">
         <f>C11*0.28</f>
-        <v/>
+        <v>82303.20000000001</v>
       </c>
       <c r="D12" s="6">
         <f>D11*0.27</f>
-        <v/>
+        <v>101233.8</v>
       </c>
     </row>
     <row r="13">
@@ -1816,15 +1846,15 @@
       </c>
       <c r="B13" s="6">
         <f>B11*0.05</f>
-        <v/>
+        <v>10747.5</v>
       </c>
       <c r="C13" s="6">
         <f>C11*0.05</f>
-        <v/>
+        <v>14697.0</v>
       </c>
       <c r="D13" s="6">
         <f>D11*0.05</f>
-        <v/>
+        <v>18747.0</v>
       </c>
     </row>
     <row r="14">
@@ -1835,15 +1865,15 @@
       </c>
       <c r="B14" s="6">
         <f>B11*0.12</f>
-        <v/>
+        <v>25794.0</v>
       </c>
       <c r="C14" s="6">
         <f>C11*0.13</f>
-        <v/>
+        <v>38212.200000000004</v>
       </c>
       <c r="D14" s="6">
         <f>D11*0.14</f>
-        <v/>
+        <v>52491.600000000006</v>
       </c>
     </row>
     <row r="15">
@@ -1870,15 +1900,15 @@
       </c>
       <c r="B16" s="9">
         <f>SUM(B12:B15)</f>
-        <v/>
+        <v>105127.5</v>
       </c>
       <c r="C16" s="9">
         <f>SUM(C12:C15)</f>
-        <v/>
+        <v>144412.40000000002</v>
       </c>
       <c r="D16" s="9">
         <f>SUM(D12:D15)</f>
-        <v/>
+        <v>183272.40000000002</v>
       </c>
     </row>
     <row r="17">
@@ -1889,15 +1919,15 @@
       </c>
       <c r="B17" s="17">
         <f>B11-B16</f>
-        <v/>
+        <v>109822.5</v>
       </c>
       <c r="C17" s="17">
         <f>C11-C16</f>
-        <v/>
+        <v>149527.59999999998</v>
       </c>
       <c r="D17" s="17">
         <f>D11-D16</f>
-        <v/>
+        <v>191667.59999999998</v>
       </c>
     </row>
     <row r="18">
@@ -1908,23 +1938,32 @@
       </c>
       <c r="B18" s="19">
         <f>B17/B11</f>
-        <v/>
+        <v>0.5109211444521982</v>
       </c>
       <c r="C18" s="19">
         <f>C17/C11</f>
-        <v/>
+        <v>0.5087010954616588</v>
       </c>
       <c r="D18" s="19">
         <f>D17/D11</f>
-        <v/>
+        <v>0.5111953912626019</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1932,7 +1971,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1955,6 +1994,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1985,7 +2025,7 @@
       </c>
       <c r="B6" s="6">
         <f>850*0.35+1850*0.65</f>
-        <v/>
+        <v>1500.0</v>
       </c>
     </row>
     <row r="7">
@@ -1996,7 +2036,7 @@
       </c>
       <c r="B7" s="7">
         <f>1-0.28-0.05-0.12</f>
-        <v/>
+        <v>0.5499999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2007,7 +2047,7 @@
       </c>
       <c r="B8" s="6">
         <f>B6*B7</f>
-        <v/>
+        <v>824.9999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2018,7 +2058,7 @@
       </c>
       <c r="B9" s="20">
         <f>B5/B8</f>
-        <v/>
+        <v>10.181818181818183</v>
       </c>
     </row>
     <row r="10">
@@ -2029,15 +2069,24 @@
       </c>
       <c r="B10" s="21">
         <f>B9/10</f>
-        <v/>
+        <v>1.0181818181818183</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2045,7 +2094,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2072,6 +2121,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2358,10 +2408,19 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2369,7 +2428,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2394,6 +2453,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2612,9 +2672,18 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>